--- a/Vaibhav_Makheja BA Project.xlsx
+++ b/Vaibhav_Makheja BA Project.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BA Project data\Vaibhav_Makheja_BA-Porject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B8F045-B71C-4394-BF11-533684EC1CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FAD405-7105-465C-B4E6-8A42431EB4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="8" xr2:uid="{4A6377C7-876D-48A4-BC1A-BCE063BA05A7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{4A6377C7-876D-48A4-BC1A-BCE063BA05A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -920,6 +920,36 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment justifyLastLine="1"/>
@@ -951,36 +981,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1383,18 +1383,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J3" s="13"/>
@@ -1881,11 +1881,11 @@
       <c r="F37" s="12"/>
     </row>
     <row r="41" spans="2:8" ht="24" x14ac:dyDescent="0.4">
-      <c r="D41" s="60" t="s">
+      <c r="D41" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
     </row>
     <row r="44" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D44" s="22" t="s">
@@ -1915,16 +1915,16 @@
       <c r="D46" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E46" s="69">
+      <c r="E46" s="57">
         <v>0.15</v>
       </c>
-      <c r="F46" s="70">
+      <c r="F46" s="58">
         <v>90000</v>
       </c>
-      <c r="G46" s="70">
+      <c r="G46" s="58">
         <v>320000</v>
       </c>
-      <c r="H46" s="70">
+      <c r="H46" s="58">
         <v>1080000</v>
       </c>
     </row>
@@ -1932,16 +1932,16 @@
       <c r="D47" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="E47" s="69">
+      <c r="E47" s="57">
         <v>0.1</v>
       </c>
-      <c r="F47" s="70">
+      <c r="F47" s="58">
         <v>60000</v>
       </c>
-      <c r="G47" s="70">
+      <c r="G47" s="58">
         <v>240000</v>
       </c>
-      <c r="H47" s="70">
+      <c r="H47" s="58">
         <v>720000</v>
       </c>
     </row>
@@ -1949,16 +1949,16 @@
       <c r="D48" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E48" s="69">
+      <c r="E48" s="57">
         <v>0.1</v>
       </c>
-      <c r="F48" s="70">
+      <c r="F48" s="58">
         <v>60000</v>
       </c>
-      <c r="G48" s="70">
+      <c r="G48" s="58">
         <v>240000</v>
       </c>
-      <c r="H48" s="70">
+      <c r="H48" s="58">
         <v>720000</v>
       </c>
     </row>
@@ -1966,16 +1966,16 @@
       <c r="D49" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="E49" s="69">
+      <c r="E49" s="57">
         <v>0.1</v>
       </c>
-      <c r="F49" s="70">
+      <c r="F49" s="58">
         <v>60000</v>
       </c>
-      <c r="G49" s="70">
+      <c r="G49" s="58">
         <v>240000</v>
       </c>
-      <c r="H49" s="70">
+      <c r="H49" s="58">
         <v>720000</v>
       </c>
     </row>
@@ -1983,16 +1983,16 @@
       <c r="D50" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="E50" s="69">
+      <c r="E50" s="57">
         <v>0.15</v>
       </c>
-      <c r="F50" s="70">
+      <c r="F50" s="58">
         <v>90000</v>
       </c>
-      <c r="G50" s="70">
+      <c r="G50" s="58">
         <v>360000</v>
       </c>
-      <c r="H50" s="70">
+      <c r="H50" s="58">
         <v>1080000</v>
       </c>
     </row>
@@ -2000,16 +2000,16 @@
       <c r="D51" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="69">
+      <c r="E51" s="57">
         <v>0.25</v>
       </c>
-      <c r="F51" s="70">
+      <c r="F51" s="58">
         <v>150000</v>
       </c>
-      <c r="G51" s="70">
+      <c r="G51" s="58">
         <v>600000</v>
       </c>
-      <c r="H51" s="70">
+      <c r="H51" s="58">
         <v>1800000</v>
       </c>
     </row>
@@ -2017,16 +2017,16 @@
       <c r="D52" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="69">
+      <c r="E52" s="57">
         <v>0.15</v>
       </c>
-      <c r="F52" s="70">
+      <c r="F52" s="58">
         <v>90000</v>
       </c>
-      <c r="G52" s="70">
+      <c r="G52" s="58">
         <v>360000</v>
       </c>
-      <c r="H52" s="70">
+      <c r="H52" s="58">
         <v>1080000</v>
       </c>
     </row>
@@ -2037,10 +2037,10 @@
       <c r="E53" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F53" s="70">
+      <c r="F53" s="58">
         <v>25000</v>
       </c>
-      <c r="G53" s="70">
+      <c r="G53" s="58">
         <v>100000</v>
       </c>
       <c r="H53" s="29" t="s">
@@ -2051,16 +2051,16 @@
       <c r="D54" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="E54" s="71">
+      <c r="E54" s="59">
         <v>1</v>
       </c>
-      <c r="F54" s="72">
+      <c r="F54" s="60">
         <v>625000</v>
       </c>
-      <c r="G54" s="72">
-        <v>2500000</v>
-      </c>
-      <c r="H54" s="72">
+      <c r="G54" s="60">
+        <v>2460000</v>
+      </c>
+      <c r="H54" s="60">
         <v>7200000</v>
       </c>
     </row>
@@ -2090,21 +2090,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C4" s="17"/>
@@ -2304,13 +2304,13 @@
     </row>
     <row r="18" spans="3:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C18" s="1"/>
-      <c r="D18" s="64" t="s">
+      <c r="D18" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.25">
@@ -2572,15 +2572,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
     </row>
     <row r="4" spans="2:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="C4" s="19" t="s">
@@ -2715,12 +2715,12 @@
       </c>
     </row>
     <row r="18" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C18" s="65" t="s">
+      <c r="C18" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
     </row>
     <row r="20" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C20" s="27" t="s">
@@ -2881,15 +2881,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:9" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
     </row>
     <row r="4" spans="3:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C4" s="23" t="s">
@@ -3043,12 +3043,12 @@
       </c>
     </row>
     <row r="18" spans="3:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C18" s="67" t="s">
+      <c r="C18" s="77" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
     </row>
     <row r="20" spans="3:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D20" s="34" t="s">
@@ -3209,15 +3209,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="72" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
     </row>
     <row r="4" spans="3:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C4" s="23" t="s">
@@ -3371,12 +3371,12 @@
       </c>
     </row>
     <row r="17" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C17" s="67" t="s">
+      <c r="C17" s="77" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="65"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
     </row>
     <row r="20" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C20" s="34" t="s">
@@ -3538,15 +3538,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:9" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="70" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
     </row>
     <row r="4" spans="3:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C4" s="33"/>
@@ -3678,12 +3678,12 @@
     </row>
     <row r="13" spans="3:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="3:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C18" s="67" t="s">
+      <c r="C18" s="77" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
     </row>
     <row r="20" spans="3:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D20" s="34" t="s">
@@ -3845,15 +3845,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
     </row>
     <row r="4" spans="3:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C4" s="23" t="s">
@@ -4007,12 +4007,12 @@
       </c>
     </row>
     <row r="18" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C18" s="67" t="s">
+      <c r="C18" s="77" t="s">
         <v>162</v>
       </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
     </row>
     <row r="20" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C20" s="34" t="s">
@@ -4174,15 +4174,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:9" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="70" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
     </row>
     <row r="4" spans="3:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C4" s="23" t="s">
@@ -4336,12 +4336,12 @@
       </c>
     </row>
     <row r="16" spans="3:9" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="77" t="s">
         <v>164</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
     </row>
     <row r="20" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C20" s="34" t="s">
@@ -4504,180 +4504,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="4" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="73" t="s">
+      <c r="D4" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="73" t="s">
+      <c r="I4" s="61" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
     </row>
     <row r="6" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="74">
+      <c r="C6" s="62">
         <v>1</v>
       </c>
-      <c r="D6" s="74" t="s">
+      <c r="D6" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="74" t="s">
+      <c r="E6" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="H6" s="78" t="s">
+      <c r="H6" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="75" t="s">
+      <c r="I6" s="63" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
     </row>
     <row r="8" spans="1:13" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="74">
+      <c r="C8" s="62">
         <v>2</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="74" t="s">
+      <c r="E8" s="62" t="s">
         <v>161</v>
       </c>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="H8" s="76" t="s">
+      <c r="H8" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="77" t="s">
+      <c r="I8" s="65" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
     </row>
     <row r="10" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="74">
+      <c r="C10" s="62">
         <v>3</v>
       </c>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="74" t="s">
+      <c r="E10" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="74" t="s">
+      <c r="F10" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="G10" s="74" t="s">
+      <c r="G10" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="H10" s="78" t="s">
+      <c r="H10" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="77" t="s">
+      <c r="I10" s="65" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
     </row>
     <row r="12" spans="1:13" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="74">
+      <c r="C12" s="62">
         <v>4</v>
       </c>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="74" t="s">
+      <c r="E12" s="62" t="s">
         <v>160</v>
       </c>
-      <c r="F12" s="74" t="s">
+      <c r="F12" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="74" t="s">
+      <c r="G12" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="H12" s="78" t="s">
+      <c r="H12" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="77" t="s">
+      <c r="I12" s="65" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="77" t="s">
         <v>163</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
     </row>
     <row r="20" spans="4:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D20" s="34" t="s">
@@ -4806,11 +4806,11 @@
         <v>165000</v>
       </c>
       <c r="F29" s="36">
-        <f t="shared" ref="F29:G29" si="0">SUM(F22:F28)</f>
+        <f>SUM(F22:F28)</f>
         <v>2360000</v>
       </c>
       <c r="G29" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F29:G29" si="0">SUM(G22:G28)</f>
         <v>7200000</v>
       </c>
     </row>
